--- a/artfynd/A 46911-2024 artfynd.xlsx
+++ b/artfynd/A 46911-2024 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121064078</v>
+        <v>121064055</v>
       </c>
       <c r="B7" t="n">
-        <v>78334</v>
+        <v>78338</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398661</v>
+        <v>398658</v>
       </c>
       <c r="R7" t="n">
-        <v>6697773</v>
+        <v>6697770</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121064926</v>
+        <v>121064918</v>
       </c>
       <c r="B8" t="n">
-        <v>79216</v>
+        <v>78338</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398636</v>
+        <v>398639</v>
       </c>
       <c r="R8" t="n">
-        <v>6697752</v>
+        <v>6697756</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121064055</v>
+        <v>121064078</v>
       </c>
       <c r="B9" t="n">
-        <v>78335</v>
+        <v>78337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398658</v>
+        <v>398661</v>
       </c>
       <c r="R9" t="n">
-        <v>6697770</v>
+        <v>6697773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121064918</v>
+        <v>121064926</v>
       </c>
       <c r="B10" t="n">
-        <v>78335</v>
+        <v>79219</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398639</v>
+        <v>398636</v>
       </c>
       <c r="R10" t="n">
-        <v>6697756</v>
+        <v>6697752</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121064922</v>
+        <v>121064849</v>
       </c>
       <c r="B11" t="n">
-        <v>78334</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398636</v>
+        <v>398664</v>
       </c>
       <c r="R11" t="n">
-        <v>6697744</v>
+        <v>6697758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121064754</v>
+        <v>121064401</v>
       </c>
       <c r="B12" t="n">
-        <v>74644</v>
+        <v>74647</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,14 +1816,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kullåsen, Kullåsen, Vrm</t>
+          <t>Slokärren, Slokärren, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398854</v>
+        <v>398793</v>
       </c>
       <c r="R12" t="n">
-        <v>6697790</v>
+        <v>6697746</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121064873</v>
+        <v>121064754</v>
       </c>
       <c r="B13" t="n">
-        <v>79216</v>
+        <v>74647</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,38 +1904,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slokärren, Slokärren, Vrm</t>
+          <t>Kullåsen, Kullåsen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398643</v>
+        <v>398854</v>
       </c>
       <c r="R13" t="n">
-        <v>6697746</v>
+        <v>6697790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121064401</v>
+        <v>121064922</v>
       </c>
       <c r="B14" t="n">
-        <v>74644</v>
+        <v>78337</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398793</v>
+        <v>398636</v>
       </c>
       <c r="R14" t="n">
-        <v>6697746</v>
+        <v>6697744</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121063954</v>
+        <v>121064661</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>56563</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,25 +2128,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398555</v>
+        <v>398876</v>
       </c>
       <c r="R15" t="n">
-        <v>6697797</v>
+        <v>6697756</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121063946</v>
+        <v>121064873</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>79219</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398561</v>
+        <v>398643</v>
       </c>
       <c r="R16" t="n">
-        <v>6697787</v>
+        <v>6697746</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121065096</v>
+        <v>121063954</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,25 +2352,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398525</v>
+        <v>398555</v>
       </c>
       <c r="R17" t="n">
-        <v>6697777</v>
+        <v>6697797</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121064661</v>
+        <v>121063946</v>
       </c>
       <c r="B18" t="n">
-        <v>56560</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398876</v>
+        <v>398561</v>
       </c>
       <c r="R18" t="n">
-        <v>6697756</v>
+        <v>6697787</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121064849</v>
+        <v>121065096</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,25 +2576,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398664</v>
+        <v>398525</v>
       </c>
       <c r="R19" t="n">
-        <v>6697758</v>
+        <v>6697777</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46911-2024 artfynd.xlsx
+++ b/artfynd/A 46911-2024 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121064055</v>
+        <v>121064926</v>
       </c>
       <c r="B7" t="n">
-        <v>78338</v>
+        <v>79219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398658</v>
+        <v>398636</v>
       </c>
       <c r="R7" t="n">
-        <v>6697770</v>
+        <v>6697752</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121064078</v>
+        <v>121064055</v>
       </c>
       <c r="B9" t="n">
-        <v>78337</v>
+        <v>78338</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398661</v>
+        <v>398658</v>
       </c>
       <c r="R9" t="n">
-        <v>6697773</v>
+        <v>6697770</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121064926</v>
+        <v>121064078</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>78337</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398636</v>
+        <v>398661</v>
       </c>
       <c r="R10" t="n">
-        <v>6697752</v>
+        <v>6697773</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121064849</v>
+        <v>121065096</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398664</v>
+        <v>398525</v>
       </c>
       <c r="R11" t="n">
-        <v>6697758</v>
+        <v>6697777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121064401</v>
+        <v>121064661</v>
       </c>
       <c r="B12" t="n">
-        <v>74647</v>
+        <v>56563</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,21 +1796,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398793</v>
+        <v>398876</v>
       </c>
       <c r="R12" t="n">
-        <v>6697746</v>
+        <v>6697756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121064922</v>
+        <v>121063954</v>
       </c>
       <c r="B14" t="n">
-        <v>78337</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398636</v>
+        <v>398555</v>
       </c>
       <c r="R14" t="n">
-        <v>6697744</v>
+        <v>6697797</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121064661</v>
+        <v>121064849</v>
       </c>
       <c r="B15" t="n">
-        <v>56563</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,25 +2128,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398876</v>
+        <v>398664</v>
       </c>
       <c r="R15" t="n">
-        <v>6697756</v>
+        <v>6697758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121064873</v>
+        <v>121064401</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>74647</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,25 +2240,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398643</v>
+        <v>398793</v>
       </c>
       <c r="R16" t="n">
         <v>6697746</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121063954</v>
+        <v>121064873</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>79219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398555</v>
+        <v>398643</v>
       </c>
       <c r="R17" t="n">
-        <v>6697797</v>
+        <v>6697746</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121065096</v>
+        <v>121064922</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>78337</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,25 +2576,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398525</v>
+        <v>398636</v>
       </c>
       <c r="R19" t="n">
-        <v>6697777</v>
+        <v>6697744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46911-2024 artfynd.xlsx
+++ b/artfynd/A 46911-2024 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>121064926</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121064918</v>
+        <v>121064055</v>
       </c>
       <c r="B8" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398639</v>
+        <v>398658</v>
       </c>
       <c r="R8" t="n">
-        <v>6697756</v>
+        <v>6697770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121064055</v>
+        <v>121064918</v>
       </c>
       <c r="B9" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398658</v>
+        <v>398639</v>
       </c>
       <c r="R9" t="n">
-        <v>6697770</v>
+        <v>6697756</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
         <v>121064078</v>
       </c>
       <c r="B10" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121065096</v>
+        <v>121064754</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>74649</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,38 +1680,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slokärren, Slokärren, Vrm</t>
+          <t>Kullåsen, Kullåsen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398525</v>
+        <v>398854</v>
       </c>
       <c r="R11" t="n">
-        <v>6697777</v>
+        <v>6697790</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121064754</v>
+        <v>121064873</v>
       </c>
       <c r="B13" t="n">
-        <v>74647</v>
+        <v>79222</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,38 +1904,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kullåsen, Kullåsen, Vrm</t>
+          <t>Slokärren, Slokärren, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398854</v>
+        <v>398643</v>
       </c>
       <c r="R13" t="n">
-        <v>6697790</v>
+        <v>6697746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121063954</v>
+        <v>121065096</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398555</v>
+        <v>398525</v>
       </c>
       <c r="R14" t="n">
-        <v>6697797</v>
+        <v>6697777</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121064849</v>
+        <v>121064401</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>74649</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,25 +2128,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398664</v>
+        <v>398793</v>
       </c>
       <c r="R15" t="n">
-        <v>6697758</v>
+        <v>6697746</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121064401</v>
+        <v>121063954</v>
       </c>
       <c r="B16" t="n">
-        <v>74647</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,25 +2240,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398793</v>
+        <v>398555</v>
       </c>
       <c r="R16" t="n">
-        <v>6697746</v>
+        <v>6697797</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121064873</v>
+        <v>121063946</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398643</v>
+        <v>398561</v>
       </c>
       <c r="R17" t="n">
-        <v>6697746</v>
+        <v>6697787</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121063946</v>
+        <v>121064849</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398561</v>
+        <v>398664</v>
       </c>
       <c r="R18" t="n">
-        <v>6697787</v>
+        <v>6697758</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,7 +2567,7 @@
         <v>121064922</v>
       </c>
       <c r="B19" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 46911-2024 artfynd.xlsx
+++ b/artfynd/A 46911-2024 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121064926</v>
+        <v>121064918</v>
       </c>
       <c r="B7" t="n">
-        <v>79222</v>
+        <v>78341</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398636</v>
+        <v>398639</v>
       </c>
       <c r="R7" t="n">
-        <v>6697752</v>
+        <v>6697756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121064918</v>
+        <v>121064078</v>
       </c>
       <c r="B9" t="n">
-        <v>78341</v>
+        <v>78340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398639</v>
+        <v>398661</v>
       </c>
       <c r="R9" t="n">
-        <v>6697756</v>
+        <v>6697773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121064078</v>
+        <v>121064926</v>
       </c>
       <c r="B10" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398661</v>
+        <v>398636</v>
       </c>
       <c r="R10" t="n">
-        <v>6697773</v>
+        <v>6697752</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121064754</v>
+        <v>121063946</v>
       </c>
       <c r="B11" t="n">
-        <v>74649</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,38 +1680,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullåsen, Kullåsen, Vrm</t>
+          <t>Slokärren, Slokärren, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398854</v>
+        <v>398561</v>
       </c>
       <c r="R11" t="n">
-        <v>6697790</v>
+        <v>6697787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121064661</v>
+        <v>121063954</v>
       </c>
       <c r="B12" t="n">
-        <v>56563</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398876</v>
+        <v>398555</v>
       </c>
       <c r="R12" t="n">
-        <v>6697756</v>
+        <v>6697797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121064873</v>
+        <v>121064401</v>
       </c>
       <c r="B13" t="n">
-        <v>79222</v>
+        <v>74649</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1904,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398643</v>
+        <v>398793</v>
       </c>
       <c r="R13" t="n">
         <v>6697746</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121065096</v>
+        <v>121064661</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>56563</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398525</v>
+        <v>398876</v>
       </c>
       <c r="R14" t="n">
-        <v>6697777</v>
+        <v>6697756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121064401</v>
+        <v>121064849</v>
       </c>
       <c r="B15" t="n">
-        <v>74649</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,25 +2128,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398793</v>
+        <v>398664</v>
       </c>
       <c r="R15" t="n">
-        <v>6697746</v>
+        <v>6697758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121063954</v>
+        <v>121064754</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>74649</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,38 +2240,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slokärren, Slokärren, Vrm</t>
+          <t>Kullåsen, Kullåsen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398555</v>
+        <v>398854</v>
       </c>
       <c r="R16" t="n">
-        <v>6697797</v>
+        <v>6697790</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121063946</v>
+        <v>121064873</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>79222</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398561</v>
+        <v>398643</v>
       </c>
       <c r="R17" t="n">
-        <v>6697787</v>
+        <v>6697746</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121064849</v>
+        <v>121065096</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398664</v>
+        <v>398525</v>
       </c>
       <c r="R18" t="n">
-        <v>6697758</v>
+        <v>6697777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 46911-2024 artfynd.xlsx
+++ b/artfynd/A 46911-2024 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>121064918</v>
       </c>
       <c r="B7" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>121064055</v>
       </c>
       <c r="B8" t="n">
-        <v>78341</v>
+        <v>78344</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>121064078</v>
       </c>
       <c r="B9" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>121064926</v>
       </c>
       <c r="B10" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121063946</v>
+        <v>121064873</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398561</v>
+        <v>398643</v>
       </c>
       <c r="R11" t="n">
-        <v>6697787</v>
+        <v>6697746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,7 +1783,7 @@
         <v>121063954</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121064401</v>
+        <v>121064922</v>
       </c>
       <c r="B13" t="n">
-        <v>74649</v>
+        <v>78343</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1904,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398793</v>
+        <v>398636</v>
       </c>
       <c r="R13" t="n">
-        <v>6697746</v>
+        <v>6697744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121064661</v>
+        <v>121064849</v>
       </c>
       <c r="B14" t="n">
-        <v>56563</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398876</v>
+        <v>398664</v>
       </c>
       <c r="R14" t="n">
-        <v>6697756</v>
+        <v>6697758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121064849</v>
+        <v>121063946</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398664</v>
+        <v>398561</v>
       </c>
       <c r="R15" t="n">
-        <v>6697758</v>
+        <v>6697787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121064754</v>
+        <v>121065096</v>
       </c>
       <c r="B16" t="n">
-        <v>74649</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,38 +2240,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullåsen, Kullåsen, Vrm</t>
+          <t>Slokärren, Slokärren, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398854</v>
+        <v>398525</v>
       </c>
       <c r="R16" t="n">
-        <v>6697790</v>
+        <v>6697777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121064873</v>
+        <v>121064661</v>
       </c>
       <c r="B17" t="n">
-        <v>79222</v>
+        <v>56566</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,25 +2352,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398643</v>
+        <v>398876</v>
       </c>
       <c r="R17" t="n">
-        <v>6697746</v>
+        <v>6697756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121065096</v>
+        <v>121064754</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>74652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,38 +2464,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slokärren, Slokärren, Vrm</t>
+          <t>Kullåsen, Kullåsen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398525</v>
+        <v>398854</v>
       </c>
       <c r="R18" t="n">
-        <v>6697777</v>
+        <v>6697790</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121064922</v>
+        <v>121064401</v>
       </c>
       <c r="B19" t="n">
-        <v>78340</v>
+        <v>74652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,25 +2576,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398636</v>
+        <v>398793</v>
       </c>
       <c r="R19" t="n">
-        <v>6697744</v>
+        <v>6697746</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46911-2024 artfynd.xlsx
+++ b/artfynd/A 46911-2024 artfynd.xlsx
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121064873</v>
+        <v>121064922</v>
       </c>
       <c r="B11" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398643</v>
+        <v>398636</v>
       </c>
       <c r="R11" t="n">
-        <v>6697746</v>
+        <v>6697744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121063954</v>
+        <v>121065096</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398555</v>
+        <v>398525</v>
       </c>
       <c r="R12" t="n">
-        <v>6697797</v>
+        <v>6697777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121064922</v>
+        <v>121064401</v>
       </c>
       <c r="B13" t="n">
-        <v>78343</v>
+        <v>74652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1904,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398636</v>
+        <v>398793</v>
       </c>
       <c r="R13" t="n">
-        <v>6697744</v>
+        <v>6697746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121064849</v>
+        <v>121064661</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>56566</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2016,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398664</v>
+        <v>398876</v>
       </c>
       <c r="R14" t="n">
-        <v>6697758</v>
+        <v>6697756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,7 +2116,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121063946</v>
+        <v>121063954</v>
       </c>
       <c r="B15" t="n">
         <v>78607</v>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>398561</v>
+        <v>398555</v>
       </c>
       <c r="R15" t="n">
-        <v>6697787</v>
+        <v>6697797</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121065096</v>
+        <v>121063946</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,25 +2240,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>398525</v>
+        <v>398561</v>
       </c>
       <c r="R16" t="n">
-        <v>6697777</v>
+        <v>6697787</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121064661</v>
+        <v>121064754</v>
       </c>
       <c r="B17" t="n">
-        <v>56566</v>
+        <v>74652</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,34 +2356,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slokärren, Slokärren, Vrm</t>
+          <t>Kullåsen, Kullåsen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>398876</v>
+        <v>398854</v>
       </c>
       <c r="R17" t="n">
-        <v>6697756</v>
+        <v>6697790</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121064754</v>
+        <v>121064873</v>
       </c>
       <c r="B18" t="n">
-        <v>74652</v>
+        <v>79225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,38 +2464,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kullåsen, Kullåsen, Vrm</t>
+          <t>Slokärren, Slokärren, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>398854</v>
+        <v>398643</v>
       </c>
       <c r="R18" t="n">
-        <v>6697790</v>
+        <v>6697746</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121064401</v>
+        <v>121064849</v>
       </c>
       <c r="B19" t="n">
-        <v>74652</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,25 +2576,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>398793</v>
+        <v>398664</v>
       </c>
       <c r="R19" t="n">
-        <v>6697746</v>
+        <v>6697758</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46911-2024 artfynd.xlsx
+++ b/artfynd/A 46911-2024 artfynd.xlsx
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121064922</v>
+        <v>121065096</v>
       </c>
       <c r="B11" t="n">
-        <v>78343</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>398636</v>
+        <v>398525</v>
       </c>
       <c r="R11" t="n">
-        <v>6697744</v>
+        <v>6697777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121065096</v>
+        <v>121064922</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>78343</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>398525</v>
+        <v>398636</v>
       </c>
       <c r="R12" t="n">
-        <v>6697777</v>
+        <v>6697744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121064401</v>
+        <v>121064661</v>
       </c>
       <c r="B13" t="n">
-        <v>74652</v>
+        <v>56566</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>398793</v>
+        <v>398876</v>
       </c>
       <c r="R13" t="n">
-        <v>6697746</v>
+        <v>6697756</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121064661</v>
+        <v>121064401</v>
       </c>
       <c r="B14" t="n">
-        <v>56566</v>
+        <v>74652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>398876</v>
+        <v>398793</v>
       </c>
       <c r="R14" t="n">
-        <v>6697756</v>
+        <v>6697746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
